--- a/ExportOrderWebServer/Resources/TemplateUploadCntrs.xlsx
+++ b/ExportOrderWebServer/Resources/TemplateUploadCntrs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Документы\_Разработчик\VS Model\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Lessons\AxionPlus\ExportOrder\ExportOrderWebServer\ExportOrderWebServer\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3186B34-0F2B-45F9-A99E-3397D5AC9369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A8D2B45-74DE-4DD1-AB60-699D7FE9DB66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="ИмпортСписка ГТД КК" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="ф310">'ИмпортСписка ГТД КК'!$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ИмпортСписка ГТД КК'!$A$1:$J$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -670,9 +670,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -710,7 +710,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -816,7 +816,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -958,7 +958,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4720,6 +4720,7 @@
       <c r="J310" s="4"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/ExportOrderWebServer/Resources/TemplateUploadCntrs.xlsx
+++ b/ExportOrderWebServer/Resources/TemplateUploadCntrs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Lessons\AxionPlus\ExportOrder\ExportOrderWebServer\ExportOrderWebServer\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6862169-9A0C-416C-B338-DFEE2CF212E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2C6E2F5-5F45-4B12-90F8-D610720BF534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,9 +16,9 @@
     <sheet name="ИмпортСписка ГТД КК" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ИмпортСписка ГТД КК'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'ИмпортСписка ГТД КК'!$A$1:$L$1</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -601,7 +601,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -628,6 +628,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1050,8 +1053,8 @@
       <c r="H2" s="3"/>
       <c r="I2" s="8"/>
       <c r="J2" s="8"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="3"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
@@ -1064,8 +1067,8 @@
       <c r="H3" s="3"/>
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="3"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
@@ -1078,8 +1081,8 @@
       <c r="H4" s="3"/>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="3"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
@@ -1092,8 +1095,8 @@
       <c r="H5" s="3"/>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="3"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
@@ -1106,8 +1109,8 @@
       <c r="H6" s="3"/>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="3"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
@@ -1120,8 +1123,8 @@
       <c r="H7" s="3"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="3"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
@@ -1134,8 +1137,8 @@
       <c r="H8" s="3"/>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="3"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
@@ -1148,8 +1151,8 @@
       <c r="H9" s="3"/>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="3"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
@@ -1162,8 +1165,8 @@
       <c r="H10" s="3"/>
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="3"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
@@ -1176,8 +1179,8 @@
       <c r="H11" s="3"/>
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="3"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
@@ -1190,8 +1193,8 @@
       <c r="H12" s="3"/>
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="3"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
@@ -1204,8 +1207,8 @@
       <c r="H13" s="3"/>
       <c r="I13" s="8"/>
       <c r="J13" s="8"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="3"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
@@ -1218,8 +1221,8 @@
       <c r="H14" s="3"/>
       <c r="I14" s="8"/>
       <c r="J14" s="8"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="3"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
@@ -1232,8 +1235,8 @@
       <c r="H15" s="3"/>
       <c r="I15" s="8"/>
       <c r="J15" s="8"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="3"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
@@ -1246,8 +1249,8 @@
       <c r="H16" s="3"/>
       <c r="I16" s="8"/>
       <c r="J16" s="8"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="3"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
@@ -1260,8 +1263,8 @@
       <c r="H17" s="3"/>
       <c r="I17" s="8"/>
       <c r="J17" s="8"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="3"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
@@ -1274,8 +1277,8 @@
       <c r="H18" s="3"/>
       <c r="I18" s="8"/>
       <c r="J18" s="8"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="3"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
@@ -1288,8 +1291,8 @@
       <c r="H19" s="3"/>
       <c r="I19" s="8"/>
       <c r="J19" s="8"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="3"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
@@ -1302,8 +1305,8 @@
       <c r="H20" s="3"/>
       <c r="I20" s="8"/>
       <c r="J20" s="8"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="3"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
@@ -1316,8 +1319,8 @@
       <c r="H21" s="3"/>
       <c r="I21" s="8"/>
       <c r="J21" s="8"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="3"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
@@ -1330,8 +1333,8 @@
       <c r="H22" s="3"/>
       <c r="I22" s="8"/>
       <c r="J22" s="8"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="3"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
@@ -1344,8 +1347,8 @@
       <c r="H23" s="3"/>
       <c r="I23" s="8"/>
       <c r="J23" s="8"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="3"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
@@ -1358,8 +1361,8 @@
       <c r="H24" s="3"/>
       <c r="I24" s="8"/>
       <c r="J24" s="8"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="3"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
@@ -1372,8 +1375,8 @@
       <c r="H25" s="3"/>
       <c r="I25" s="8"/>
       <c r="J25" s="8"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="3"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
@@ -1386,8 +1389,8 @@
       <c r="H26" s="3"/>
       <c r="I26" s="8"/>
       <c r="J26" s="8"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="3"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="10"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
@@ -1400,8 +1403,8 @@
       <c r="H27" s="3"/>
       <c r="I27" s="8"/>
       <c r="J27" s="8"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="3"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
@@ -1414,8 +1417,8 @@
       <c r="H28" s="3"/>
       <c r="I28" s="8"/>
       <c r="J28" s="8"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="3"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
@@ -1428,8 +1431,8 @@
       <c r="H29" s="3"/>
       <c r="I29" s="8"/>
       <c r="J29" s="8"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="3"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
@@ -1442,8 +1445,8 @@
       <c r="H30" s="3"/>
       <c r="I30" s="8"/>
       <c r="J30" s="8"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="3"/>
+      <c r="K30" s="10"/>
+      <c r="L30" s="10"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
@@ -1456,8 +1459,8 @@
       <c r="H31" s="3"/>
       <c r="I31" s="8"/>
       <c r="J31" s="8"/>
-      <c r="K31" s="9"/>
-      <c r="L31" s="3"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="10"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
@@ -1470,8 +1473,8 @@
       <c r="H32" s="3"/>
       <c r="I32" s="8"/>
       <c r="J32" s="8"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="3"/>
+      <c r="K32" s="10"/>
+      <c r="L32" s="10"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
@@ -1484,8 +1487,8 @@
       <c r="H33" s="3"/>
       <c r="I33" s="8"/>
       <c r="J33" s="8"/>
-      <c r="K33" s="9"/>
-      <c r="L33" s="3"/>
+      <c r="K33" s="10"/>
+      <c r="L33" s="10"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
@@ -1498,8 +1501,8 @@
       <c r="H34" s="3"/>
       <c r="I34" s="8"/>
       <c r="J34" s="8"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="3"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="10"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
@@ -1512,8 +1515,8 @@
       <c r="H35" s="3"/>
       <c r="I35" s="8"/>
       <c r="J35" s="8"/>
-      <c r="K35" s="9"/>
-      <c r="L35" s="3"/>
+      <c r="K35" s="10"/>
+      <c r="L35" s="10"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
@@ -1526,8 +1529,8 @@
       <c r="H36" s="3"/>
       <c r="I36" s="8"/>
       <c r="J36" s="8"/>
-      <c r="K36" s="9"/>
-      <c r="L36" s="3"/>
+      <c r="K36" s="10"/>
+      <c r="L36" s="10"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
@@ -1540,8 +1543,8 @@
       <c r="H37" s="3"/>
       <c r="I37" s="8"/>
       <c r="J37" s="8"/>
-      <c r="K37" s="9"/>
-      <c r="L37" s="3"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
@@ -1554,8 +1557,8 @@
       <c r="H38" s="3"/>
       <c r="I38" s="8"/>
       <c r="J38" s="8"/>
-      <c r="K38" s="9"/>
-      <c r="L38" s="3"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
@@ -1568,8 +1571,8 @@
       <c r="H39" s="3"/>
       <c r="I39" s="8"/>
       <c r="J39" s="8"/>
-      <c r="K39" s="9"/>
-      <c r="L39" s="3"/>
+      <c r="K39" s="10"/>
+      <c r="L39" s="10"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
@@ -1582,8 +1585,8 @@
       <c r="H40" s="3"/>
       <c r="I40" s="8"/>
       <c r="J40" s="8"/>
-      <c r="K40" s="9"/>
-      <c r="L40" s="3"/>
+      <c r="K40" s="10"/>
+      <c r="L40" s="10"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
@@ -1596,8 +1599,8 @@
       <c r="H41" s="3"/>
       <c r="I41" s="8"/>
       <c r="J41" s="8"/>
-      <c r="K41" s="9"/>
-      <c r="L41" s="3"/>
+      <c r="K41" s="10"/>
+      <c r="L41" s="10"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
@@ -1610,8 +1613,8 @@
       <c r="H42" s="3"/>
       <c r="I42" s="8"/>
       <c r="J42" s="8"/>
-      <c r="K42" s="9"/>
-      <c r="L42" s="3"/>
+      <c r="K42" s="10"/>
+      <c r="L42" s="10"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="5"/>
@@ -1624,8 +1627,8 @@
       <c r="H43" s="3"/>
       <c r="I43" s="8"/>
       <c r="J43" s="8"/>
-      <c r="K43" s="9"/>
-      <c r="L43" s="3"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
@@ -1638,8 +1641,8 @@
       <c r="H44" s="3"/>
       <c r="I44" s="8"/>
       <c r="J44" s="8"/>
-      <c r="K44" s="9"/>
-      <c r="L44" s="3"/>
+      <c r="K44" s="10"/>
+      <c r="L44" s="10"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="5"/>
@@ -1652,8 +1655,8 @@
       <c r="H45" s="3"/>
       <c r="I45" s="8"/>
       <c r="J45" s="8"/>
-      <c r="K45" s="9"/>
-      <c r="L45" s="3"/>
+      <c r="K45" s="10"/>
+      <c r="L45" s="10"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="5"/>
@@ -1666,8 +1669,8 @@
       <c r="H46" s="3"/>
       <c r="I46" s="8"/>
       <c r="J46" s="8"/>
-      <c r="K46" s="9"/>
-      <c r="L46" s="3"/>
+      <c r="K46" s="10"/>
+      <c r="L46" s="10"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="5"/>
@@ -1680,8 +1683,8 @@
       <c r="H47" s="3"/>
       <c r="I47" s="8"/>
       <c r="J47" s="8"/>
-      <c r="K47" s="9"/>
-      <c r="L47" s="3"/>
+      <c r="K47" s="10"/>
+      <c r="L47" s="10"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="5"/>
@@ -1694,8 +1697,8 @@
       <c r="H48" s="3"/>
       <c r="I48" s="8"/>
       <c r="J48" s="8"/>
-      <c r="K48" s="9"/>
-      <c r="L48" s="3"/>
+      <c r="K48" s="10"/>
+      <c r="L48" s="10"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="5"/>
@@ -1708,8 +1711,8 @@
       <c r="H49" s="3"/>
       <c r="I49" s="8"/>
       <c r="J49" s="8"/>
-      <c r="K49" s="9"/>
-      <c r="L49" s="3"/>
+      <c r="K49" s="10"/>
+      <c r="L49" s="10"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="5"/>
@@ -1722,8 +1725,8 @@
       <c r="H50" s="3"/>
       <c r="I50" s="8"/>
       <c r="J50" s="8"/>
-      <c r="K50" s="9"/>
-      <c r="L50" s="3"/>
+      <c r="K50" s="10"/>
+      <c r="L50" s="10"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="5"/>
@@ -1736,8 +1739,8 @@
       <c r="H51" s="3"/>
       <c r="I51" s="8"/>
       <c r="J51" s="8"/>
-      <c r="K51" s="9"/>
-      <c r="L51" s="3"/>
+      <c r="K51" s="10"/>
+      <c r="L51" s="10"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
@@ -1750,8 +1753,8 @@
       <c r="H52" s="3"/>
       <c r="I52" s="8"/>
       <c r="J52" s="8"/>
-      <c r="K52" s="9"/>
-      <c r="L52" s="3"/>
+      <c r="K52" s="10"/>
+      <c r="L52" s="10"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="5"/>
@@ -1764,8 +1767,8 @@
       <c r="H53" s="3"/>
       <c r="I53" s="8"/>
       <c r="J53" s="8"/>
-      <c r="K53" s="9"/>
-      <c r="L53" s="3"/>
+      <c r="K53" s="10"/>
+      <c r="L53" s="10"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="5"/>
@@ -1778,8 +1781,8 @@
       <c r="H54" s="3"/>
       <c r="I54" s="8"/>
       <c r="J54" s="8"/>
-      <c r="K54" s="9"/>
-      <c r="L54" s="3"/>
+      <c r="K54" s="10"/>
+      <c r="L54" s="10"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="5"/>
@@ -1792,8 +1795,8 @@
       <c r="H55" s="3"/>
       <c r="I55" s="8"/>
       <c r="J55" s="8"/>
-      <c r="K55" s="9"/>
-      <c r="L55" s="3"/>
+      <c r="K55" s="10"/>
+      <c r="L55" s="10"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="5"/>
@@ -1806,8 +1809,8 @@
       <c r="H56" s="3"/>
       <c r="I56" s="8"/>
       <c r="J56" s="8"/>
-      <c r="K56" s="9"/>
-      <c r="L56" s="3"/>
+      <c r="K56" s="10"/>
+      <c r="L56" s="10"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="5"/>
@@ -1820,8 +1823,8 @@
       <c r="H57" s="3"/>
       <c r="I57" s="8"/>
       <c r="J57" s="8"/>
-      <c r="K57" s="9"/>
-      <c r="L57" s="3"/>
+      <c r="K57" s="10"/>
+      <c r="L57" s="10"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="5"/>
@@ -1834,8 +1837,8 @@
       <c r="H58" s="3"/>
       <c r="I58" s="8"/>
       <c r="J58" s="8"/>
-      <c r="K58" s="9"/>
-      <c r="L58" s="3"/>
+      <c r="K58" s="10"/>
+      <c r="L58" s="10"/>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="5"/>
@@ -1848,8 +1851,8 @@
       <c r="H59" s="3"/>
       <c r="I59" s="8"/>
       <c r="J59" s="8"/>
-      <c r="K59" s="9"/>
-      <c r="L59" s="3"/>
+      <c r="K59" s="10"/>
+      <c r="L59" s="10"/>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="5"/>
@@ -1862,8 +1865,8 @@
       <c r="H60" s="3"/>
       <c r="I60" s="8"/>
       <c r="J60" s="8"/>
-      <c r="K60" s="9"/>
-      <c r="L60" s="3"/>
+      <c r="K60" s="10"/>
+      <c r="L60" s="10"/>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
@@ -1876,8 +1879,8 @@
       <c r="H61" s="3"/>
       <c r="I61" s="8"/>
       <c r="J61" s="8"/>
-      <c r="K61" s="9"/>
-      <c r="L61" s="3"/>
+      <c r="K61" s="10"/>
+      <c r="L61" s="10"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="5"/>
@@ -1890,8 +1893,8 @@
       <c r="H62" s="3"/>
       <c r="I62" s="8"/>
       <c r="J62" s="8"/>
-      <c r="K62" s="9"/>
-      <c r="L62" s="3"/>
+      <c r="K62" s="10"/>
+      <c r="L62" s="10"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="5"/>
@@ -1904,8 +1907,8 @@
       <c r="H63" s="3"/>
       <c r="I63" s="8"/>
       <c r="J63" s="8"/>
-      <c r="K63" s="9"/>
-      <c r="L63" s="3"/>
+      <c r="K63" s="10"/>
+      <c r="L63" s="10"/>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="5"/>
@@ -1918,8 +1921,8 @@
       <c r="H64" s="3"/>
       <c r="I64" s="8"/>
       <c r="J64" s="8"/>
-      <c r="K64" s="9"/>
-      <c r="L64" s="3"/>
+      <c r="K64" s="10"/>
+      <c r="L64" s="10"/>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="5"/>
@@ -1932,8 +1935,8 @@
       <c r="H65" s="3"/>
       <c r="I65" s="8"/>
       <c r="J65" s="8"/>
-      <c r="K65" s="9"/>
-      <c r="L65" s="3"/>
+      <c r="K65" s="10"/>
+      <c r="L65" s="10"/>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="5"/>
@@ -1946,8 +1949,8 @@
       <c r="H66" s="3"/>
       <c r="I66" s="8"/>
       <c r="J66" s="8"/>
-      <c r="K66" s="9"/>
-      <c r="L66" s="3"/>
+      <c r="K66" s="10"/>
+      <c r="L66" s="10"/>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="5"/>
@@ -1960,8 +1963,8 @@
       <c r="H67" s="3"/>
       <c r="I67" s="8"/>
       <c r="J67" s="8"/>
-      <c r="K67" s="9"/>
-      <c r="L67" s="3"/>
+      <c r="K67" s="10"/>
+      <c r="L67" s="10"/>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="5"/>
@@ -1974,8 +1977,8 @@
       <c r="H68" s="3"/>
       <c r="I68" s="8"/>
       <c r="J68" s="8"/>
-      <c r="K68" s="9"/>
-      <c r="L68" s="3"/>
+      <c r="K68" s="10"/>
+      <c r="L68" s="10"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="5"/>
@@ -1988,8 +1991,8 @@
       <c r="H69" s="3"/>
       <c r="I69" s="8"/>
       <c r="J69" s="8"/>
-      <c r="K69" s="9"/>
-      <c r="L69" s="3"/>
+      <c r="K69" s="10"/>
+      <c r="L69" s="10"/>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="5"/>
@@ -2002,8 +2005,8 @@
       <c r="H70" s="3"/>
       <c r="I70" s="8"/>
       <c r="J70" s="8"/>
-      <c r="K70" s="9"/>
-      <c r="L70" s="3"/>
+      <c r="K70" s="10"/>
+      <c r="L70" s="10"/>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="5"/>
@@ -2016,8 +2019,8 @@
       <c r="H71" s="3"/>
       <c r="I71" s="8"/>
       <c r="J71" s="8"/>
-      <c r="K71" s="9"/>
-      <c r="L71" s="3"/>
+      <c r="K71" s="10"/>
+      <c r="L71" s="10"/>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="5"/>
@@ -2030,8 +2033,8 @@
       <c r="H72" s="3"/>
       <c r="I72" s="8"/>
       <c r="J72" s="8"/>
-      <c r="K72" s="9"/>
-      <c r="L72" s="3"/>
+      <c r="K72" s="10"/>
+      <c r="L72" s="10"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="5"/>
@@ -2044,8 +2047,8 @@
       <c r="H73" s="3"/>
       <c r="I73" s="8"/>
       <c r="J73" s="8"/>
-      <c r="K73" s="9"/>
-      <c r="L73" s="3"/>
+      <c r="K73" s="10"/>
+      <c r="L73" s="10"/>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="5"/>
@@ -2058,8 +2061,8 @@
       <c r="H74" s="3"/>
       <c r="I74" s="8"/>
       <c r="J74" s="8"/>
-      <c r="K74" s="9"/>
-      <c r="L74" s="3"/>
+      <c r="K74" s="10"/>
+      <c r="L74" s="10"/>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="5"/>
@@ -2072,8 +2075,8 @@
       <c r="H75" s="3"/>
       <c r="I75" s="8"/>
       <c r="J75" s="8"/>
-      <c r="K75" s="9"/>
-      <c r="L75" s="3"/>
+      <c r="K75" s="10"/>
+      <c r="L75" s="10"/>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="5"/>
@@ -2086,8 +2089,8 @@
       <c r="H76" s="3"/>
       <c r="I76" s="8"/>
       <c r="J76" s="8"/>
-      <c r="K76" s="9"/>
-      <c r="L76" s="3"/>
+      <c r="K76" s="10"/>
+      <c r="L76" s="10"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="5"/>
@@ -2100,8 +2103,8 @@
       <c r="H77" s="3"/>
       <c r="I77" s="8"/>
       <c r="J77" s="8"/>
-      <c r="K77" s="9"/>
-      <c r="L77" s="3"/>
+      <c r="K77" s="10"/>
+      <c r="L77" s="10"/>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="5"/>
@@ -2114,8 +2117,8 @@
       <c r="H78" s="3"/>
       <c r="I78" s="8"/>
       <c r="J78" s="8"/>
-      <c r="K78" s="9"/>
-      <c r="L78" s="3"/>
+      <c r="K78" s="10"/>
+      <c r="L78" s="10"/>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="5"/>
@@ -2128,8 +2131,8 @@
       <c r="H79" s="3"/>
       <c r="I79" s="8"/>
       <c r="J79" s="8"/>
-      <c r="K79" s="9"/>
-      <c r="L79" s="3"/>
+      <c r="K79" s="10"/>
+      <c r="L79" s="10"/>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" s="5"/>
@@ -2142,8 +2145,8 @@
       <c r="H80" s="3"/>
       <c r="I80" s="8"/>
       <c r="J80" s="8"/>
-      <c r="K80" s="9"/>
-      <c r="L80" s="3"/>
+      <c r="K80" s="10"/>
+      <c r="L80" s="10"/>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" s="5"/>
@@ -2156,8 +2159,8 @@
       <c r="H81" s="3"/>
       <c r="I81" s="8"/>
       <c r="J81" s="8"/>
-      <c r="K81" s="9"/>
-      <c r="L81" s="3"/>
+      <c r="K81" s="10"/>
+      <c r="L81" s="10"/>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="5"/>
@@ -2170,8 +2173,8 @@
       <c r="H82" s="3"/>
       <c r="I82" s="8"/>
       <c r="J82" s="8"/>
-      <c r="K82" s="9"/>
-      <c r="L82" s="3"/>
+      <c r="K82" s="10"/>
+      <c r="L82" s="10"/>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" s="5"/>
@@ -2184,8 +2187,8 @@
       <c r="H83" s="3"/>
       <c r="I83" s="8"/>
       <c r="J83" s="8"/>
-      <c r="K83" s="9"/>
-      <c r="L83" s="3"/>
+      <c r="K83" s="10"/>
+      <c r="L83" s="10"/>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" s="5"/>
@@ -2198,8 +2201,8 @@
       <c r="H84" s="3"/>
       <c r="I84" s="8"/>
       <c r="J84" s="8"/>
-      <c r="K84" s="9"/>
-      <c r="L84" s="3"/>
+      <c r="K84" s="10"/>
+      <c r="L84" s="10"/>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" s="5"/>
@@ -2212,8 +2215,8 @@
       <c r="H85" s="3"/>
       <c r="I85" s="8"/>
       <c r="J85" s="8"/>
-      <c r="K85" s="9"/>
-      <c r="L85" s="3"/>
+      <c r="K85" s="10"/>
+      <c r="L85" s="10"/>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" s="5"/>
@@ -2226,8 +2229,8 @@
       <c r="H86" s="3"/>
       <c r="I86" s="8"/>
       <c r="J86" s="8"/>
-      <c r="K86" s="9"/>
-      <c r="L86" s="3"/>
+      <c r="K86" s="10"/>
+      <c r="L86" s="10"/>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" s="5"/>
@@ -2240,8 +2243,8 @@
       <c r="H87" s="3"/>
       <c r="I87" s="8"/>
       <c r="J87" s="8"/>
-      <c r="K87" s="9"/>
-      <c r="L87" s="3"/>
+      <c r="K87" s="10"/>
+      <c r="L87" s="10"/>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" s="5"/>
@@ -2254,8 +2257,8 @@
       <c r="H88" s="3"/>
       <c r="I88" s="8"/>
       <c r="J88" s="8"/>
-      <c r="K88" s="9"/>
-      <c r="L88" s="3"/>
+      <c r="K88" s="10"/>
+      <c r="L88" s="10"/>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" s="5"/>
@@ -2268,8 +2271,8 @@
       <c r="H89" s="3"/>
       <c r="I89" s="8"/>
       <c r="J89" s="8"/>
-      <c r="K89" s="9"/>
-      <c r="L89" s="3"/>
+      <c r="K89" s="10"/>
+      <c r="L89" s="10"/>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" s="5"/>
@@ -2282,8 +2285,8 @@
       <c r="H90" s="3"/>
       <c r="I90" s="8"/>
       <c r="J90" s="8"/>
-      <c r="K90" s="9"/>
-      <c r="L90" s="3"/>
+      <c r="K90" s="10"/>
+      <c r="L90" s="10"/>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" s="5"/>
@@ -2296,8 +2299,8 @@
       <c r="H91" s="3"/>
       <c r="I91" s="8"/>
       <c r="J91" s="8"/>
-      <c r="K91" s="9"/>
-      <c r="L91" s="3"/>
+      <c r="K91" s="10"/>
+      <c r="L91" s="10"/>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" s="5"/>
@@ -2310,8 +2313,8 @@
       <c r="H92" s="3"/>
       <c r="I92" s="8"/>
       <c r="J92" s="8"/>
-      <c r="K92" s="9"/>
-      <c r="L92" s="3"/>
+      <c r="K92" s="10"/>
+      <c r="L92" s="10"/>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" s="5"/>
@@ -2324,8 +2327,8 @@
       <c r="H93" s="3"/>
       <c r="I93" s="8"/>
       <c r="J93" s="8"/>
-      <c r="K93" s="9"/>
-      <c r="L93" s="3"/>
+      <c r="K93" s="10"/>
+      <c r="L93" s="10"/>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" s="5"/>
@@ -2338,8 +2341,8 @@
       <c r="H94" s="3"/>
       <c r="I94" s="8"/>
       <c r="J94" s="8"/>
-      <c r="K94" s="9"/>
-      <c r="L94" s="3"/>
+      <c r="K94" s="10"/>
+      <c r="L94" s="10"/>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" s="5"/>
@@ -2352,8 +2355,8 @@
       <c r="H95" s="3"/>
       <c r="I95" s="8"/>
       <c r="J95" s="8"/>
-      <c r="K95" s="9"/>
-      <c r="L95" s="3"/>
+      <c r="K95" s="10"/>
+      <c r="L95" s="10"/>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" s="5"/>
@@ -2366,8 +2369,8 @@
       <c r="H96" s="3"/>
       <c r="I96" s="8"/>
       <c r="J96" s="8"/>
-      <c r="K96" s="9"/>
-      <c r="L96" s="3"/>
+      <c r="K96" s="10"/>
+      <c r="L96" s="10"/>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" s="5"/>
@@ -2380,8 +2383,8 @@
       <c r="H97" s="3"/>
       <c r="I97" s="8"/>
       <c r="J97" s="8"/>
-      <c r="K97" s="9"/>
-      <c r="L97" s="3"/>
+      <c r="K97" s="10"/>
+      <c r="L97" s="10"/>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" s="5"/>
@@ -2394,8 +2397,8 @@
       <c r="H98" s="3"/>
       <c r="I98" s="8"/>
       <c r="J98" s="8"/>
-      <c r="K98" s="9"/>
-      <c r="L98" s="3"/>
+      <c r="K98" s="10"/>
+      <c r="L98" s="10"/>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="5"/>
@@ -2408,8 +2411,8 @@
       <c r="H99" s="3"/>
       <c r="I99" s="8"/>
       <c r="J99" s="8"/>
-      <c r="K99" s="9"/>
-      <c r="L99" s="3"/>
+      <c r="K99" s="10"/>
+      <c r="L99" s="10"/>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" s="5"/>
@@ -2422,8 +2425,8 @@
       <c r="H100" s="3"/>
       <c r="I100" s="8"/>
       <c r="J100" s="8"/>
-      <c r="K100" s="9"/>
-      <c r="L100" s="3"/>
+      <c r="K100" s="10"/>
+      <c r="L100" s="10"/>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" s="5"/>
@@ -2436,8 +2439,8 @@
       <c r="H101" s="3"/>
       <c r="I101" s="8"/>
       <c r="J101" s="8"/>
-      <c r="K101" s="9"/>
-      <c r="L101" s="3"/>
+      <c r="K101" s="10"/>
+      <c r="L101" s="10"/>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" s="5"/>
@@ -2450,8 +2453,8 @@
       <c r="H102" s="3"/>
       <c r="I102" s="8"/>
       <c r="J102" s="8"/>
-      <c r="K102" s="9"/>
-      <c r="L102" s="3"/>
+      <c r="K102" s="10"/>
+      <c r="L102" s="10"/>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" s="5"/>
@@ -2464,8 +2467,8 @@
       <c r="H103" s="3"/>
       <c r="I103" s="8"/>
       <c r="J103" s="8"/>
-      <c r="K103" s="9"/>
-      <c r="L103" s="3"/>
+      <c r="K103" s="10"/>
+      <c r="L103" s="10"/>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" s="5"/>
@@ -2478,8 +2481,8 @@
       <c r="H104" s="3"/>
       <c r="I104" s="8"/>
       <c r="J104" s="8"/>
-      <c r="K104" s="9"/>
-      <c r="L104" s="3"/>
+      <c r="K104" s="10"/>
+      <c r="L104" s="10"/>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" s="5"/>
@@ -2492,8 +2495,8 @@
       <c r="H105" s="3"/>
       <c r="I105" s="8"/>
       <c r="J105" s="8"/>
-      <c r="K105" s="9"/>
-      <c r="L105" s="3"/>
+      <c r="K105" s="10"/>
+      <c r="L105" s="10"/>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" s="5"/>
@@ -2506,8 +2509,8 @@
       <c r="H106" s="3"/>
       <c r="I106" s="8"/>
       <c r="J106" s="8"/>
-      <c r="K106" s="9"/>
-      <c r="L106" s="3"/>
+      <c r="K106" s="10"/>
+      <c r="L106" s="10"/>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107" s="5"/>
@@ -2520,8 +2523,8 @@
       <c r="H107" s="3"/>
       <c r="I107" s="8"/>
       <c r="J107" s="8"/>
-      <c r="K107" s="9"/>
-      <c r="L107" s="3"/>
+      <c r="K107" s="10"/>
+      <c r="L107" s="10"/>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" s="5"/>
@@ -2534,8 +2537,8 @@
       <c r="H108" s="3"/>
       <c r="I108" s="8"/>
       <c r="J108" s="8"/>
-      <c r="K108" s="9"/>
-      <c r="L108" s="3"/>
+      <c r="K108" s="10"/>
+      <c r="L108" s="10"/>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" s="5"/>
@@ -2548,8 +2551,8 @@
       <c r="H109" s="3"/>
       <c r="I109" s="8"/>
       <c r="J109" s="8"/>
-      <c r="K109" s="9"/>
-      <c r="L109" s="3"/>
+      <c r="K109" s="10"/>
+      <c r="L109" s="10"/>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110" s="5"/>
@@ -2562,8 +2565,8 @@
       <c r="H110" s="3"/>
       <c r="I110" s="8"/>
       <c r="J110" s="8"/>
-      <c r="K110" s="9"/>
-      <c r="L110" s="3"/>
+      <c r="K110" s="10"/>
+      <c r="L110" s="10"/>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111" s="5"/>
@@ -2576,8 +2579,8 @@
       <c r="H111" s="3"/>
       <c r="I111" s="8"/>
       <c r="J111" s="8"/>
-      <c r="K111" s="9"/>
-      <c r="L111" s="3"/>
+      <c r="K111" s="10"/>
+      <c r="L111" s="10"/>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112" s="5"/>
@@ -2590,8 +2593,8 @@
       <c r="H112" s="3"/>
       <c r="I112" s="8"/>
       <c r="J112" s="8"/>
-      <c r="K112" s="9"/>
-      <c r="L112" s="3"/>
+      <c r="K112" s="10"/>
+      <c r="L112" s="10"/>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" s="5"/>
@@ -2604,8 +2607,8 @@
       <c r="H113" s="3"/>
       <c r="I113" s="8"/>
       <c r="J113" s="8"/>
-      <c r="K113" s="9"/>
-      <c r="L113" s="3"/>
+      <c r="K113" s="10"/>
+      <c r="L113" s="10"/>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" s="5"/>
@@ -2618,8 +2621,8 @@
       <c r="H114" s="3"/>
       <c r="I114" s="8"/>
       <c r="J114" s="8"/>
-      <c r="K114" s="9"/>
-      <c r="L114" s="3"/>
+      <c r="K114" s="10"/>
+      <c r="L114" s="10"/>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" s="5"/>
@@ -2632,8 +2635,8 @@
       <c r="H115" s="3"/>
       <c r="I115" s="8"/>
       <c r="J115" s="8"/>
-      <c r="K115" s="9"/>
-      <c r="L115" s="3"/>
+      <c r="K115" s="10"/>
+      <c r="L115" s="10"/>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" s="5"/>
@@ -2646,8 +2649,8 @@
       <c r="H116" s="3"/>
       <c r="I116" s="8"/>
       <c r="J116" s="8"/>
-      <c r="K116" s="9"/>
-      <c r="L116" s="3"/>
+      <c r="K116" s="10"/>
+      <c r="L116" s="10"/>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" s="5"/>
@@ -2660,8 +2663,8 @@
       <c r="H117" s="3"/>
       <c r="I117" s="8"/>
       <c r="J117" s="8"/>
-      <c r="K117" s="9"/>
-      <c r="L117" s="3"/>
+      <c r="K117" s="10"/>
+      <c r="L117" s="10"/>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" s="5"/>
@@ -2674,8 +2677,8 @@
       <c r="H118" s="3"/>
       <c r="I118" s="8"/>
       <c r="J118" s="8"/>
-      <c r="K118" s="9"/>
-      <c r="L118" s="3"/>
+      <c r="K118" s="10"/>
+      <c r="L118" s="10"/>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" s="5"/>
@@ -2688,8 +2691,8 @@
       <c r="H119" s="3"/>
       <c r="I119" s="8"/>
       <c r="J119" s="8"/>
-      <c r="K119" s="9"/>
-      <c r="L119" s="3"/>
+      <c r="K119" s="10"/>
+      <c r="L119" s="10"/>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" s="5"/>
@@ -2702,8 +2705,8 @@
       <c r="H120" s="3"/>
       <c r="I120" s="8"/>
       <c r="J120" s="8"/>
-      <c r="K120" s="9"/>
-      <c r="L120" s="3"/>
+      <c r="K120" s="10"/>
+      <c r="L120" s="10"/>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121" s="5"/>
@@ -2716,8 +2719,8 @@
       <c r="H121" s="3"/>
       <c r="I121" s="8"/>
       <c r="J121" s="8"/>
-      <c r="K121" s="9"/>
-      <c r="L121" s="3"/>
+      <c r="K121" s="10"/>
+      <c r="L121" s="10"/>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" s="5"/>
@@ -2730,8 +2733,8 @@
       <c r="H122" s="3"/>
       <c r="I122" s="8"/>
       <c r="J122" s="8"/>
-      <c r="K122" s="9"/>
-      <c r="L122" s="3"/>
+      <c r="K122" s="10"/>
+      <c r="L122" s="10"/>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" s="5"/>
@@ -2744,8 +2747,8 @@
       <c r="H123" s="3"/>
       <c r="I123" s="8"/>
       <c r="J123" s="8"/>
-      <c r="K123" s="9"/>
-      <c r="L123" s="3"/>
+      <c r="K123" s="10"/>
+      <c r="L123" s="10"/>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" s="5"/>
@@ -2758,8 +2761,8 @@
       <c r="H124" s="3"/>
       <c r="I124" s="8"/>
       <c r="J124" s="8"/>
-      <c r="K124" s="9"/>
-      <c r="L124" s="3"/>
+      <c r="K124" s="10"/>
+      <c r="L124" s="10"/>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" s="5"/>
@@ -2772,8 +2775,8 @@
       <c r="H125" s="3"/>
       <c r="I125" s="8"/>
       <c r="J125" s="8"/>
-      <c r="K125" s="9"/>
-      <c r="L125" s="3"/>
+      <c r="K125" s="10"/>
+      <c r="L125" s="10"/>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" s="5"/>
@@ -2786,8 +2789,8 @@
       <c r="H126" s="3"/>
       <c r="I126" s="8"/>
       <c r="J126" s="8"/>
-      <c r="K126" s="9"/>
-      <c r="L126" s="3"/>
+      <c r="K126" s="10"/>
+      <c r="L126" s="10"/>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" s="5"/>
@@ -2800,8 +2803,8 @@
       <c r="H127" s="3"/>
       <c r="I127" s="8"/>
       <c r="J127" s="8"/>
-      <c r="K127" s="9"/>
-      <c r="L127" s="3"/>
+      <c r="K127" s="10"/>
+      <c r="L127" s="10"/>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" s="5"/>
@@ -2814,8 +2817,8 @@
       <c r="H128" s="3"/>
       <c r="I128" s="8"/>
       <c r="J128" s="8"/>
-      <c r="K128" s="9"/>
-      <c r="L128" s="3"/>
+      <c r="K128" s="10"/>
+      <c r="L128" s="10"/>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" s="5"/>
@@ -2828,8 +2831,8 @@
       <c r="H129" s="3"/>
       <c r="I129" s="8"/>
       <c r="J129" s="8"/>
-      <c r="K129" s="9"/>
-      <c r="L129" s="3"/>
+      <c r="K129" s="10"/>
+      <c r="L129" s="10"/>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130" s="5"/>
@@ -2842,8 +2845,8 @@
       <c r="H130" s="3"/>
       <c r="I130" s="8"/>
       <c r="J130" s="8"/>
-      <c r="K130" s="9"/>
-      <c r="L130" s="3"/>
+      <c r="K130" s="10"/>
+      <c r="L130" s="10"/>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" s="5"/>
@@ -2856,8 +2859,8 @@
       <c r="H131" s="3"/>
       <c r="I131" s="8"/>
       <c r="J131" s="8"/>
-      <c r="K131" s="9"/>
-      <c r="L131" s="3"/>
+      <c r="K131" s="10"/>
+      <c r="L131" s="10"/>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" s="5"/>
@@ -2870,8 +2873,8 @@
       <c r="H132" s="3"/>
       <c r="I132" s="8"/>
       <c r="J132" s="8"/>
-      <c r="K132" s="9"/>
-      <c r="L132" s="3"/>
+      <c r="K132" s="10"/>
+      <c r="L132" s="10"/>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133" s="5"/>
@@ -2884,8 +2887,8 @@
       <c r="H133" s="3"/>
       <c r="I133" s="8"/>
       <c r="J133" s="8"/>
-      <c r="K133" s="9"/>
-      <c r="L133" s="3"/>
+      <c r="K133" s="10"/>
+      <c r="L133" s="10"/>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134" s="5"/>
@@ -2898,8 +2901,8 @@
       <c r="H134" s="3"/>
       <c r="I134" s="8"/>
       <c r="J134" s="8"/>
-      <c r="K134" s="9"/>
-      <c r="L134" s="3"/>
+      <c r="K134" s="10"/>
+      <c r="L134" s="10"/>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" s="5"/>
@@ -2912,8 +2915,8 @@
       <c r="H135" s="3"/>
       <c r="I135" s="8"/>
       <c r="J135" s="8"/>
-      <c r="K135" s="9"/>
-      <c r="L135" s="3"/>
+      <c r="K135" s="10"/>
+      <c r="L135" s="10"/>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136" s="5"/>
@@ -2926,8 +2929,8 @@
       <c r="H136" s="3"/>
       <c r="I136" s="8"/>
       <c r="J136" s="8"/>
-      <c r="K136" s="9"/>
-      <c r="L136" s="3"/>
+      <c r="K136" s="10"/>
+      <c r="L136" s="10"/>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" s="5"/>
@@ -2940,8 +2943,8 @@
       <c r="H137" s="3"/>
       <c r="I137" s="8"/>
       <c r="J137" s="8"/>
-      <c r="K137" s="9"/>
-      <c r="L137" s="3"/>
+      <c r="K137" s="10"/>
+      <c r="L137" s="10"/>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" s="5"/>
@@ -2954,8 +2957,8 @@
       <c r="H138" s="3"/>
       <c r="I138" s="8"/>
       <c r="J138" s="8"/>
-      <c r="K138" s="9"/>
-      <c r="L138" s="3"/>
+      <c r="K138" s="10"/>
+      <c r="L138" s="10"/>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" s="5"/>
@@ -2968,8 +2971,8 @@
       <c r="H139" s="3"/>
       <c r="I139" s="8"/>
       <c r="J139" s="8"/>
-      <c r="K139" s="9"/>
-      <c r="L139" s="3"/>
+      <c r="K139" s="10"/>
+      <c r="L139" s="10"/>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140" s="5"/>
@@ -2982,8 +2985,8 @@
       <c r="H140" s="3"/>
       <c r="I140" s="8"/>
       <c r="J140" s="8"/>
-      <c r="K140" s="9"/>
-      <c r="L140" s="3"/>
+      <c r="K140" s="10"/>
+      <c r="L140" s="10"/>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" s="5"/>
@@ -2996,8 +2999,8 @@
       <c r="H141" s="3"/>
       <c r="I141" s="8"/>
       <c r="J141" s="8"/>
-      <c r="K141" s="9"/>
-      <c r="L141" s="3"/>
+      <c r="K141" s="10"/>
+      <c r="L141" s="10"/>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" s="5"/>
@@ -3010,8 +3013,8 @@
       <c r="H142" s="3"/>
       <c r="I142" s="8"/>
       <c r="J142" s="8"/>
-      <c r="K142" s="9"/>
-      <c r="L142" s="3"/>
+      <c r="K142" s="10"/>
+      <c r="L142" s="10"/>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" s="5"/>
@@ -3024,8 +3027,8 @@
       <c r="H143" s="3"/>
       <c r="I143" s="8"/>
       <c r="J143" s="8"/>
-      <c r="K143" s="9"/>
-      <c r="L143" s="3"/>
+      <c r="K143" s="10"/>
+      <c r="L143" s="10"/>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" s="5"/>
@@ -3038,8 +3041,8 @@
       <c r="H144" s="3"/>
       <c r="I144" s="8"/>
       <c r="J144" s="8"/>
-      <c r="K144" s="9"/>
-      <c r="L144" s="3"/>
+      <c r="K144" s="10"/>
+      <c r="L144" s="10"/>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" s="5"/>
@@ -3052,8 +3055,8 @@
       <c r="H145" s="3"/>
       <c r="I145" s="8"/>
       <c r="J145" s="8"/>
-      <c r="K145" s="9"/>
-      <c r="L145" s="3"/>
+      <c r="K145" s="10"/>
+      <c r="L145" s="10"/>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146" s="5"/>
@@ -3066,8 +3069,8 @@
       <c r="H146" s="3"/>
       <c r="I146" s="8"/>
       <c r="J146" s="8"/>
-      <c r="K146" s="9"/>
-      <c r="L146" s="3"/>
+      <c r="K146" s="10"/>
+      <c r="L146" s="10"/>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147" s="5"/>
@@ -3080,8 +3083,8 @@
       <c r="H147" s="3"/>
       <c r="I147" s="8"/>
       <c r="J147" s="8"/>
-      <c r="K147" s="9"/>
-      <c r="L147" s="3"/>
+      <c r="K147" s="10"/>
+      <c r="L147" s="10"/>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148" s="5"/>
@@ -3094,8 +3097,8 @@
       <c r="H148" s="3"/>
       <c r="I148" s="8"/>
       <c r="J148" s="8"/>
-      <c r="K148" s="9"/>
-      <c r="L148" s="3"/>
+      <c r="K148" s="10"/>
+      <c r="L148" s="10"/>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" s="5"/>
@@ -3108,8 +3111,8 @@
       <c r="H149" s="3"/>
       <c r="I149" s="8"/>
       <c r="J149" s="8"/>
-      <c r="K149" s="9"/>
-      <c r="L149" s="3"/>
+      <c r="K149" s="10"/>
+      <c r="L149" s="10"/>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" s="5"/>
@@ -3122,8 +3125,8 @@
       <c r="H150" s="3"/>
       <c r="I150" s="8"/>
       <c r="J150" s="8"/>
-      <c r="K150" s="9"/>
-      <c r="L150" s="3"/>
+      <c r="K150" s="10"/>
+      <c r="L150" s="10"/>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151" s="5"/>
@@ -3136,8 +3139,8 @@
       <c r="H151" s="3"/>
       <c r="I151" s="8"/>
       <c r="J151" s="8"/>
-      <c r="K151" s="9"/>
-      <c r="L151" s="3"/>
+      <c r="K151" s="10"/>
+      <c r="L151" s="10"/>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152" s="5"/>
@@ -3150,8 +3153,8 @@
       <c r="H152" s="3"/>
       <c r="I152" s="8"/>
       <c r="J152" s="8"/>
-      <c r="K152" s="9"/>
-      <c r="L152" s="3"/>
+      <c r="K152" s="10"/>
+      <c r="L152" s="10"/>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" s="5"/>
@@ -3164,8 +3167,8 @@
       <c r="H153" s="3"/>
       <c r="I153" s="8"/>
       <c r="J153" s="8"/>
-      <c r="K153" s="9"/>
-      <c r="L153" s="3"/>
+      <c r="K153" s="10"/>
+      <c r="L153" s="10"/>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154" s="5"/>
@@ -3178,8 +3181,8 @@
       <c r="H154" s="3"/>
       <c r="I154" s="8"/>
       <c r="J154" s="8"/>
-      <c r="K154" s="9"/>
-      <c r="L154" s="3"/>
+      <c r="K154" s="10"/>
+      <c r="L154" s="10"/>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155" s="5"/>
@@ -3192,8 +3195,8 @@
       <c r="H155" s="3"/>
       <c r="I155" s="8"/>
       <c r="J155" s="8"/>
-      <c r="K155" s="9"/>
-      <c r="L155" s="3"/>
+      <c r="K155" s="10"/>
+      <c r="L155" s="10"/>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156" s="5"/>
@@ -3206,8 +3209,8 @@
       <c r="H156" s="3"/>
       <c r="I156" s="8"/>
       <c r="J156" s="8"/>
-      <c r="K156" s="9"/>
-      <c r="L156" s="3"/>
+      <c r="K156" s="10"/>
+      <c r="L156" s="10"/>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" s="5"/>
@@ -3220,8 +3223,8 @@
       <c r="H157" s="3"/>
       <c r="I157" s="8"/>
       <c r="J157" s="8"/>
-      <c r="K157" s="9"/>
-      <c r="L157" s="3"/>
+      <c r="K157" s="10"/>
+      <c r="L157" s="10"/>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158" s="5"/>
@@ -3234,8 +3237,8 @@
       <c r="H158" s="3"/>
       <c r="I158" s="8"/>
       <c r="J158" s="8"/>
-      <c r="K158" s="9"/>
-      <c r="L158" s="3"/>
+      <c r="K158" s="10"/>
+      <c r="L158" s="10"/>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159" s="5"/>
@@ -3248,8 +3251,8 @@
       <c r="H159" s="3"/>
       <c r="I159" s="8"/>
       <c r="J159" s="8"/>
-      <c r="K159" s="9"/>
-      <c r="L159" s="3"/>
+      <c r="K159" s="10"/>
+      <c r="L159" s="10"/>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160" s="5"/>
@@ -3262,8 +3265,8 @@
       <c r="H160" s="3"/>
       <c r="I160" s="8"/>
       <c r="J160" s="8"/>
-      <c r="K160" s="9"/>
-      <c r="L160" s="3"/>
+      <c r="K160" s="10"/>
+      <c r="L160" s="10"/>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" s="5"/>
@@ -3276,8 +3279,8 @@
       <c r="H161" s="3"/>
       <c r="I161" s="8"/>
       <c r="J161" s="8"/>
-      <c r="K161" s="9"/>
-      <c r="L161" s="3"/>
+      <c r="K161" s="10"/>
+      <c r="L161" s="10"/>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" s="5"/>
@@ -3290,8 +3293,8 @@
       <c r="H162" s="3"/>
       <c r="I162" s="8"/>
       <c r="J162" s="8"/>
-      <c r="K162" s="9"/>
-      <c r="L162" s="3"/>
+      <c r="K162" s="10"/>
+      <c r="L162" s="10"/>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" s="5"/>
@@ -3304,8 +3307,8 @@
       <c r="H163" s="3"/>
       <c r="I163" s="8"/>
       <c r="J163" s="8"/>
-      <c r="K163" s="9"/>
-      <c r="L163" s="3"/>
+      <c r="K163" s="10"/>
+      <c r="L163" s="10"/>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" s="5"/>
@@ -3318,8 +3321,8 @@
       <c r="H164" s="3"/>
       <c r="I164" s="8"/>
       <c r="J164" s="8"/>
-      <c r="K164" s="9"/>
-      <c r="L164" s="3"/>
+      <c r="K164" s="10"/>
+      <c r="L164" s="10"/>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" s="5"/>
@@ -3332,8 +3335,8 @@
       <c r="H165" s="3"/>
       <c r="I165" s="8"/>
       <c r="J165" s="8"/>
-      <c r="K165" s="9"/>
-      <c r="L165" s="3"/>
+      <c r="K165" s="10"/>
+      <c r="L165" s="10"/>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" s="5"/>
@@ -3346,8 +3349,8 @@
       <c r="H166" s="3"/>
       <c r="I166" s="8"/>
       <c r="J166" s="8"/>
-      <c r="K166" s="9"/>
-      <c r="L166" s="3"/>
+      <c r="K166" s="10"/>
+      <c r="L166" s="10"/>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" s="5"/>
@@ -3360,8 +3363,8 @@
       <c r="H167" s="3"/>
       <c r="I167" s="8"/>
       <c r="J167" s="8"/>
-      <c r="K167" s="9"/>
-      <c r="L167" s="3"/>
+      <c r="K167" s="10"/>
+      <c r="L167" s="10"/>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" s="5"/>
@@ -3374,8 +3377,8 @@
       <c r="H168" s="3"/>
       <c r="I168" s="8"/>
       <c r="J168" s="8"/>
-      <c r="K168" s="9"/>
-      <c r="L168" s="3"/>
+      <c r="K168" s="10"/>
+      <c r="L168" s="10"/>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169" s="5"/>
@@ -3388,8 +3391,8 @@
       <c r="H169" s="3"/>
       <c r="I169" s="8"/>
       <c r="J169" s="8"/>
-      <c r="K169" s="9"/>
-      <c r="L169" s="3"/>
+      <c r="K169" s="10"/>
+      <c r="L169" s="10"/>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A170" s="5"/>
@@ -3402,8 +3405,8 @@
       <c r="H170" s="3"/>
       <c r="I170" s="8"/>
       <c r="J170" s="8"/>
-      <c r="K170" s="9"/>
-      <c r="L170" s="3"/>
+      <c r="K170" s="10"/>
+      <c r="L170" s="10"/>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A171" s="5"/>
@@ -3416,8 +3419,8 @@
       <c r="H171" s="3"/>
       <c r="I171" s="8"/>
       <c r="J171" s="8"/>
-      <c r="K171" s="9"/>
-      <c r="L171" s="3"/>
+      <c r="K171" s="10"/>
+      <c r="L171" s="10"/>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A172" s="5"/>
@@ -3430,8 +3433,8 @@
       <c r="H172" s="3"/>
       <c r="I172" s="8"/>
       <c r="J172" s="8"/>
-      <c r="K172" s="9"/>
-      <c r="L172" s="3"/>
+      <c r="K172" s="10"/>
+      <c r="L172" s="10"/>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A173" s="5"/>
@@ -3444,8 +3447,8 @@
       <c r="H173" s="3"/>
       <c r="I173" s="8"/>
       <c r="J173" s="8"/>
-      <c r="K173" s="9"/>
-      <c r="L173" s="3"/>
+      <c r="K173" s="10"/>
+      <c r="L173" s="10"/>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A174" s="5"/>
@@ -3458,8 +3461,8 @@
       <c r="H174" s="3"/>
       <c r="I174" s="8"/>
       <c r="J174" s="8"/>
-      <c r="K174" s="9"/>
-      <c r="L174" s="3"/>
+      <c r="K174" s="10"/>
+      <c r="L174" s="10"/>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A175" s="5"/>
@@ -3472,8 +3475,8 @@
       <c r="H175" s="3"/>
       <c r="I175" s="8"/>
       <c r="J175" s="8"/>
-      <c r="K175" s="9"/>
-      <c r="L175" s="3"/>
+      <c r="K175" s="10"/>
+      <c r="L175" s="10"/>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A176" s="5"/>
@@ -3486,8 +3489,8 @@
       <c r="H176" s="3"/>
       <c r="I176" s="8"/>
       <c r="J176" s="8"/>
-      <c r="K176" s="9"/>
-      <c r="L176" s="3"/>
+      <c r="K176" s="10"/>
+      <c r="L176" s="10"/>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A177" s="5"/>
@@ -3500,8 +3503,8 @@
       <c r="H177" s="3"/>
       <c r="I177" s="8"/>
       <c r="J177" s="8"/>
-      <c r="K177" s="9"/>
-      <c r="L177" s="3"/>
+      <c r="K177" s="10"/>
+      <c r="L177" s="10"/>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A178" s="5"/>
@@ -3514,8 +3517,8 @@
       <c r="H178" s="3"/>
       <c r="I178" s="8"/>
       <c r="J178" s="8"/>
-      <c r="K178" s="9"/>
-      <c r="L178" s="3"/>
+      <c r="K178" s="10"/>
+      <c r="L178" s="10"/>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A179" s="5"/>
@@ -3528,8 +3531,8 @@
       <c r="H179" s="3"/>
       <c r="I179" s="8"/>
       <c r="J179" s="8"/>
-      <c r="K179" s="9"/>
-      <c r="L179" s="3"/>
+      <c r="K179" s="10"/>
+      <c r="L179" s="10"/>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A180" s="5"/>
@@ -3542,8 +3545,8 @@
       <c r="H180" s="3"/>
       <c r="I180" s="8"/>
       <c r="J180" s="8"/>
-      <c r="K180" s="9"/>
-      <c r="L180" s="3"/>
+      <c r="K180" s="10"/>
+      <c r="L180" s="10"/>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A181" s="5"/>
@@ -3556,8 +3559,8 @@
       <c r="H181" s="3"/>
       <c r="I181" s="8"/>
       <c r="J181" s="8"/>
-      <c r="K181" s="9"/>
-      <c r="L181" s="3"/>
+      <c r="K181" s="10"/>
+      <c r="L181" s="10"/>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A182" s="5"/>
@@ -3570,8 +3573,8 @@
       <c r="H182" s="3"/>
       <c r="I182" s="8"/>
       <c r="J182" s="8"/>
-      <c r="K182" s="9"/>
-      <c r="L182" s="3"/>
+      <c r="K182" s="10"/>
+      <c r="L182" s="10"/>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A183" s="5"/>
@@ -3584,8 +3587,8 @@
       <c r="H183" s="3"/>
       <c r="I183" s="8"/>
       <c r="J183" s="8"/>
-      <c r="K183" s="9"/>
-      <c r="L183" s="3"/>
+      <c r="K183" s="10"/>
+      <c r="L183" s="10"/>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A184" s="5"/>
@@ -3598,8 +3601,8 @@
       <c r="H184" s="3"/>
       <c r="I184" s="8"/>
       <c r="J184" s="8"/>
-      <c r="K184" s="9"/>
-      <c r="L184" s="3"/>
+      <c r="K184" s="10"/>
+      <c r="L184" s="10"/>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A185" s="5"/>
@@ -3612,8 +3615,8 @@
       <c r="H185" s="3"/>
       <c r="I185" s="8"/>
       <c r="J185" s="8"/>
-      <c r="K185" s="9"/>
-      <c r="L185" s="3"/>
+      <c r="K185" s="10"/>
+      <c r="L185" s="10"/>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A186" s="5"/>
@@ -3626,8 +3629,8 @@
       <c r="H186" s="3"/>
       <c r="I186" s="8"/>
       <c r="J186" s="8"/>
-      <c r="K186" s="9"/>
-      <c r="L186" s="3"/>
+      <c r="K186" s="10"/>
+      <c r="L186" s="10"/>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A187" s="5"/>
@@ -3640,8 +3643,8 @@
       <c r="H187" s="3"/>
       <c r="I187" s="8"/>
       <c r="J187" s="8"/>
-      <c r="K187" s="9"/>
-      <c r="L187" s="3"/>
+      <c r="K187" s="10"/>
+      <c r="L187" s="10"/>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A188" s="5"/>
@@ -3654,8 +3657,8 @@
       <c r="H188" s="3"/>
       <c r="I188" s="8"/>
       <c r="J188" s="8"/>
-      <c r="K188" s="9"/>
-      <c r="L188" s="3"/>
+      <c r="K188" s="10"/>
+      <c r="L188" s="10"/>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A189" s="5"/>
@@ -3668,8 +3671,8 @@
       <c r="H189" s="3"/>
       <c r="I189" s="8"/>
       <c r="J189" s="8"/>
-      <c r="K189" s="9"/>
-      <c r="L189" s="3"/>
+      <c r="K189" s="10"/>
+      <c r="L189" s="10"/>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A190" s="5"/>
@@ -3682,8 +3685,8 @@
       <c r="H190" s="3"/>
       <c r="I190" s="8"/>
       <c r="J190" s="8"/>
-      <c r="K190" s="9"/>
-      <c r="L190" s="3"/>
+      <c r="K190" s="10"/>
+      <c r="L190" s="10"/>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A191" s="5"/>
@@ -3696,8 +3699,8 @@
       <c r="H191" s="3"/>
       <c r="I191" s="8"/>
       <c r="J191" s="8"/>
-      <c r="K191" s="9"/>
-      <c r="L191" s="3"/>
+      <c r="K191" s="10"/>
+      <c r="L191" s="10"/>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A192" s="5"/>
@@ -3710,8 +3713,8 @@
       <c r="H192" s="3"/>
       <c r="I192" s="8"/>
       <c r="J192" s="8"/>
-      <c r="K192" s="9"/>
-      <c r="L192" s="3"/>
+      <c r="K192" s="10"/>
+      <c r="L192" s="10"/>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A193" s="5"/>
@@ -3724,8 +3727,8 @@
       <c r="H193" s="3"/>
       <c r="I193" s="8"/>
       <c r="J193" s="8"/>
-      <c r="K193" s="9"/>
-      <c r="L193" s="3"/>
+      <c r="K193" s="10"/>
+      <c r="L193" s="10"/>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A194" s="5"/>
@@ -3738,8 +3741,8 @@
       <c r="H194" s="3"/>
       <c r="I194" s="8"/>
       <c r="J194" s="8"/>
-      <c r="K194" s="9"/>
-      <c r="L194" s="3"/>
+      <c r="K194" s="10"/>
+      <c r="L194" s="10"/>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A195" s="5"/>
@@ -3752,8 +3755,8 @@
       <c r="H195" s="3"/>
       <c r="I195" s="8"/>
       <c r="J195" s="8"/>
-      <c r="K195" s="9"/>
-      <c r="L195" s="3"/>
+      <c r="K195" s="10"/>
+      <c r="L195" s="10"/>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A196" s="5"/>
@@ -3766,8 +3769,8 @@
       <c r="H196" s="3"/>
       <c r="I196" s="8"/>
       <c r="J196" s="8"/>
-      <c r="K196" s="9"/>
-      <c r="L196" s="3"/>
+      <c r="K196" s="10"/>
+      <c r="L196" s="10"/>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A197" s="5"/>
@@ -3780,8 +3783,8 @@
       <c r="H197" s="3"/>
       <c r="I197" s="8"/>
       <c r="J197" s="8"/>
-      <c r="K197" s="9"/>
-      <c r="L197" s="3"/>
+      <c r="K197" s="10"/>
+      <c r="L197" s="10"/>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A198" s="5"/>
@@ -3794,8 +3797,8 @@
       <c r="H198" s="3"/>
       <c r="I198" s="8"/>
       <c r="J198" s="8"/>
-      <c r="K198" s="9"/>
-      <c r="L198" s="3"/>
+      <c r="K198" s="10"/>
+      <c r="L198" s="10"/>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A199" s="5"/>
@@ -3808,8 +3811,8 @@
       <c r="H199" s="3"/>
       <c r="I199" s="8"/>
       <c r="J199" s="8"/>
-      <c r="K199" s="9"/>
-      <c r="L199" s="3"/>
+      <c r="K199" s="10"/>
+      <c r="L199" s="10"/>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A200" s="5"/>
@@ -3822,8 +3825,8 @@
       <c r="H200" s="3"/>
       <c r="I200" s="8"/>
       <c r="J200" s="8"/>
-      <c r="K200" s="9"/>
-      <c r="L200" s="3"/>
+      <c r="K200" s="10"/>
+      <c r="L200" s="10"/>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A201" s="5"/>
@@ -3836,8 +3839,8 @@
       <c r="H201" s="3"/>
       <c r="I201" s="8"/>
       <c r="J201" s="8"/>
-      <c r="K201" s="9"/>
-      <c r="L201" s="3"/>
+      <c r="K201" s="10"/>
+      <c r="L201" s="10"/>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A202" s="5"/>
@@ -3850,8 +3853,8 @@
       <c r="H202" s="3"/>
       <c r="I202" s="8"/>
       <c r="J202" s="8"/>
-      <c r="K202" s="9"/>
-      <c r="L202" s="3"/>
+      <c r="K202" s="10"/>
+      <c r="L202" s="10"/>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A203" s="5"/>
@@ -3864,8 +3867,8 @@
       <c r="H203" s="3"/>
       <c r="I203" s="8"/>
       <c r="J203" s="8"/>
-      <c r="K203" s="9"/>
-      <c r="L203" s="3"/>
+      <c r="K203" s="10"/>
+      <c r="L203" s="10"/>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A204" s="5"/>
@@ -3878,8 +3881,8 @@
       <c r="H204" s="3"/>
       <c r="I204" s="8"/>
       <c r="J204" s="8"/>
-      <c r="K204" s="9"/>
-      <c r="L204" s="3"/>
+      <c r="K204" s="10"/>
+      <c r="L204" s="10"/>
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A205" s="5"/>
@@ -3892,8 +3895,8 @@
       <c r="H205" s="3"/>
       <c r="I205" s="8"/>
       <c r="J205" s="8"/>
-      <c r="K205" s="9"/>
-      <c r="L205" s="3"/>
+      <c r="K205" s="10"/>
+      <c r="L205" s="10"/>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A206" s="5"/>
@@ -3906,8 +3909,8 @@
       <c r="H206" s="3"/>
       <c r="I206" s="8"/>
       <c r="J206" s="8"/>
-      <c r="K206" s="9"/>
-      <c r="L206" s="3"/>
+      <c r="K206" s="10"/>
+      <c r="L206" s="10"/>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A207" s="5"/>
@@ -3920,8 +3923,8 @@
       <c r="H207" s="3"/>
       <c r="I207" s="8"/>
       <c r="J207" s="8"/>
-      <c r="K207" s="9"/>
-      <c r="L207" s="3"/>
+      <c r="K207" s="10"/>
+      <c r="L207" s="10"/>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A208" s="5"/>
@@ -3934,8 +3937,8 @@
       <c r="H208" s="3"/>
       <c r="I208" s="8"/>
       <c r="J208" s="8"/>
-      <c r="K208" s="9"/>
-      <c r="L208" s="3"/>
+      <c r="K208" s="10"/>
+      <c r="L208" s="10"/>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A209" s="5"/>
@@ -3948,8 +3951,8 @@
       <c r="H209" s="3"/>
       <c r="I209" s="8"/>
       <c r="J209" s="8"/>
-      <c r="K209" s="9"/>
-      <c r="L209" s="3"/>
+      <c r="K209" s="10"/>
+      <c r="L209" s="10"/>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A210" s="5"/>
@@ -3962,8 +3965,8 @@
       <c r="H210" s="3"/>
       <c r="I210" s="8"/>
       <c r="J210" s="8"/>
-      <c r="K210" s="9"/>
-      <c r="L210" s="3"/>
+      <c r="K210" s="10"/>
+      <c r="L210" s="10"/>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A211" s="5"/>
@@ -3976,8 +3979,8 @@
       <c r="H211" s="3"/>
       <c r="I211" s="8"/>
       <c r="J211" s="8"/>
-      <c r="K211" s="9"/>
-      <c r="L211" s="3"/>
+      <c r="K211" s="10"/>
+      <c r="L211" s="10"/>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A212" s="5"/>
@@ -3990,8 +3993,8 @@
       <c r="H212" s="3"/>
       <c r="I212" s="8"/>
       <c r="J212" s="8"/>
-      <c r="K212" s="9"/>
-      <c r="L212" s="3"/>
+      <c r="K212" s="10"/>
+      <c r="L212" s="10"/>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A213" s="5"/>
@@ -4004,8 +4007,8 @@
       <c r="H213" s="3"/>
       <c r="I213" s="8"/>
       <c r="J213" s="8"/>
-      <c r="K213" s="9"/>
-      <c r="L213" s="3"/>
+      <c r="K213" s="10"/>
+      <c r="L213" s="10"/>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A214" s="5"/>
@@ -4018,8 +4021,8 @@
       <c r="H214" s="3"/>
       <c r="I214" s="8"/>
       <c r="J214" s="8"/>
-      <c r="K214" s="9"/>
-      <c r="L214" s="3"/>
+      <c r="K214" s="10"/>
+      <c r="L214" s="10"/>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A215" s="5"/>
@@ -4032,8 +4035,8 @@
       <c r="H215" s="3"/>
       <c r="I215" s="8"/>
       <c r="J215" s="8"/>
-      <c r="K215" s="9"/>
-      <c r="L215" s="3"/>
+      <c r="K215" s="10"/>
+      <c r="L215" s="10"/>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A216" s="5"/>
@@ -4046,8 +4049,8 @@
       <c r="H216" s="3"/>
       <c r="I216" s="8"/>
       <c r="J216" s="8"/>
-      <c r="K216" s="9"/>
-      <c r="L216" s="3"/>
+      <c r="K216" s="10"/>
+      <c r="L216" s="10"/>
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A217" s="5"/>
@@ -4060,8 +4063,8 @@
       <c r="H217" s="3"/>
       <c r="I217" s="8"/>
       <c r="J217" s="8"/>
-      <c r="K217" s="9"/>
-      <c r="L217" s="3"/>
+      <c r="K217" s="10"/>
+      <c r="L217" s="10"/>
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A218" s="5"/>
@@ -4074,8 +4077,8 @@
       <c r="H218" s="3"/>
       <c r="I218" s="8"/>
       <c r="J218" s="8"/>
-      <c r="K218" s="9"/>
-      <c r="L218" s="3"/>
+      <c r="K218" s="10"/>
+      <c r="L218" s="10"/>
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A219" s="5"/>
@@ -4088,8 +4091,8 @@
       <c r="H219" s="3"/>
       <c r="I219" s="8"/>
       <c r="J219" s="8"/>
-      <c r="K219" s="9"/>
-      <c r="L219" s="3"/>
+      <c r="K219" s="10"/>
+      <c r="L219" s="10"/>
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A220" s="5"/>
@@ -4102,8 +4105,8 @@
       <c r="H220" s="3"/>
       <c r="I220" s="8"/>
       <c r="J220" s="8"/>
-      <c r="K220" s="9"/>
-      <c r="L220" s="3"/>
+      <c r="K220" s="10"/>
+      <c r="L220" s="10"/>
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A221" s="5"/>
@@ -4116,8 +4119,8 @@
       <c r="H221" s="3"/>
       <c r="I221" s="8"/>
       <c r="J221" s="8"/>
-      <c r="K221" s="9"/>
-      <c r="L221" s="3"/>
+      <c r="K221" s="10"/>
+      <c r="L221" s="10"/>
     </row>
     <row r="222" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A222" s="5"/>
@@ -4130,8 +4133,8 @@
       <c r="H222" s="3"/>
       <c r="I222" s="8"/>
       <c r="J222" s="8"/>
-      <c r="K222" s="9"/>
-      <c r="L222" s="3"/>
+      <c r="K222" s="10"/>
+      <c r="L222" s="10"/>
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A223" s="5"/>
@@ -4144,8 +4147,8 @@
       <c r="H223" s="3"/>
       <c r="I223" s="8"/>
       <c r="J223" s="8"/>
-      <c r="K223" s="9"/>
-      <c r="L223" s="3"/>
+      <c r="K223" s="10"/>
+      <c r="L223" s="10"/>
     </row>
     <row r="224" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A224" s="5"/>
@@ -4158,8 +4161,8 @@
       <c r="H224" s="3"/>
       <c r="I224" s="8"/>
       <c r="J224" s="8"/>
-      <c r="K224" s="9"/>
-      <c r="L224" s="3"/>
+      <c r="K224" s="10"/>
+      <c r="L224" s="10"/>
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A225" s="5"/>
@@ -4172,8 +4175,8 @@
       <c r="H225" s="3"/>
       <c r="I225" s="8"/>
       <c r="J225" s="8"/>
-      <c r="K225" s="9"/>
-      <c r="L225" s="3"/>
+      <c r="K225" s="10"/>
+      <c r="L225" s="10"/>
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A226" s="5"/>
@@ -4186,8 +4189,8 @@
       <c r="H226" s="3"/>
       <c r="I226" s="8"/>
       <c r="J226" s="8"/>
-      <c r="K226" s="9"/>
-      <c r="L226" s="3"/>
+      <c r="K226" s="10"/>
+      <c r="L226" s="10"/>
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A227" s="5"/>
@@ -4200,8 +4203,8 @@
       <c r="H227" s="3"/>
       <c r="I227" s="8"/>
       <c r="J227" s="8"/>
-      <c r="K227" s="9"/>
-      <c r="L227" s="3"/>
+      <c r="K227" s="10"/>
+      <c r="L227" s="10"/>
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A228" s="5"/>
@@ -4214,8 +4217,8 @@
       <c r="H228" s="3"/>
       <c r="I228" s="8"/>
       <c r="J228" s="8"/>
-      <c r="K228" s="9"/>
-      <c r="L228" s="3"/>
+      <c r="K228" s="10"/>
+      <c r="L228" s="10"/>
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A229" s="5"/>
@@ -4228,8 +4231,8 @@
       <c r="H229" s="3"/>
       <c r="I229" s="8"/>
       <c r="J229" s="8"/>
-      <c r="K229" s="9"/>
-      <c r="L229" s="3"/>
+      <c r="K229" s="10"/>
+      <c r="L229" s="10"/>
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A230" s="5"/>
@@ -4242,8 +4245,8 @@
       <c r="H230" s="3"/>
       <c r="I230" s="8"/>
       <c r="J230" s="8"/>
-      <c r="K230" s="9"/>
-      <c r="L230" s="3"/>
+      <c r="K230" s="10"/>
+      <c r="L230" s="10"/>
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A231" s="5"/>
@@ -4256,8 +4259,8 @@
       <c r="H231" s="3"/>
       <c r="I231" s="8"/>
       <c r="J231" s="8"/>
-      <c r="K231" s="9"/>
-      <c r="L231" s="3"/>
+      <c r="K231" s="10"/>
+      <c r="L231" s="10"/>
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A232" s="5"/>
@@ -4270,8 +4273,8 @@
       <c r="H232" s="3"/>
       <c r="I232" s="8"/>
       <c r="J232" s="8"/>
-      <c r="K232" s="9"/>
-      <c r="L232" s="3"/>
+      <c r="K232" s="10"/>
+      <c r="L232" s="10"/>
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A233" s="5"/>
@@ -4284,8 +4287,8 @@
       <c r="H233" s="3"/>
       <c r="I233" s="8"/>
       <c r="J233" s="8"/>
-      <c r="K233" s="9"/>
-      <c r="L233" s="3"/>
+      <c r="K233" s="10"/>
+      <c r="L233" s="10"/>
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A234" s="5"/>
@@ -4298,8 +4301,8 @@
       <c r="H234" s="3"/>
       <c r="I234" s="8"/>
       <c r="J234" s="8"/>
-      <c r="K234" s="9"/>
-      <c r="L234" s="3"/>
+      <c r="K234" s="10"/>
+      <c r="L234" s="10"/>
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A235" s="5"/>
@@ -4312,8 +4315,8 @@
       <c r="H235" s="3"/>
       <c r="I235" s="8"/>
       <c r="J235" s="8"/>
-      <c r="K235" s="9"/>
-      <c r="L235" s="3"/>
+      <c r="K235" s="10"/>
+      <c r="L235" s="10"/>
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A236" s="5"/>
@@ -4326,8 +4329,8 @@
       <c r="H236" s="3"/>
       <c r="I236" s="8"/>
       <c r="J236" s="8"/>
-      <c r="K236" s="9"/>
-      <c r="L236" s="3"/>
+      <c r="K236" s="10"/>
+      <c r="L236" s="10"/>
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A237" s="5"/>
@@ -4340,8 +4343,8 @@
       <c r="H237" s="3"/>
       <c r="I237" s="8"/>
       <c r="J237" s="8"/>
-      <c r="K237" s="9"/>
-      <c r="L237" s="3"/>
+      <c r="K237" s="10"/>
+      <c r="L237" s="10"/>
     </row>
     <row r="238" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A238" s="5"/>
@@ -4354,8 +4357,8 @@
       <c r="H238" s="3"/>
       <c r="I238" s="8"/>
       <c r="J238" s="8"/>
-      <c r="K238" s="9"/>
-      <c r="L238" s="3"/>
+      <c r="K238" s="10"/>
+      <c r="L238" s="10"/>
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A239" s="5"/>
@@ -4368,8 +4371,8 @@
       <c r="H239" s="3"/>
       <c r="I239" s="8"/>
       <c r="J239" s="8"/>
-      <c r="K239" s="9"/>
-      <c r="L239" s="3"/>
+      <c r="K239" s="10"/>
+      <c r="L239" s="10"/>
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A240" s="5"/>
@@ -4382,8 +4385,8 @@
       <c r="H240" s="3"/>
       <c r="I240" s="8"/>
       <c r="J240" s="8"/>
-      <c r="K240" s="9"/>
-      <c r="L240" s="3"/>
+      <c r="K240" s="10"/>
+      <c r="L240" s="10"/>
     </row>
     <row r="241" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A241" s="5"/>
@@ -4396,8 +4399,8 @@
       <c r="H241" s="3"/>
       <c r="I241" s="8"/>
       <c r="J241" s="8"/>
-      <c r="K241" s="9"/>
-      <c r="L241" s="3"/>
+      <c r="K241" s="10"/>
+      <c r="L241" s="10"/>
     </row>
     <row r="242" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A242" s="5"/>
@@ -4410,8 +4413,8 @@
       <c r="H242" s="3"/>
       <c r="I242" s="8"/>
       <c r="J242" s="8"/>
-      <c r="K242" s="9"/>
-      <c r="L242" s="3"/>
+      <c r="K242" s="10"/>
+      <c r="L242" s="10"/>
     </row>
     <row r="243" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A243" s="5"/>
@@ -4424,8 +4427,8 @@
       <c r="H243" s="3"/>
       <c r="I243" s="8"/>
       <c r="J243" s="8"/>
-      <c r="K243" s="9"/>
-      <c r="L243" s="3"/>
+      <c r="K243" s="10"/>
+      <c r="L243" s="10"/>
     </row>
     <row r="244" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A244" s="5"/>
@@ -4438,8 +4441,8 @@
       <c r="H244" s="3"/>
       <c r="I244" s="8"/>
       <c r="J244" s="8"/>
-      <c r="K244" s="9"/>
-      <c r="L244" s="3"/>
+      <c r="K244" s="10"/>
+      <c r="L244" s="10"/>
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A245" s="5"/>
@@ -4452,8 +4455,8 @@
       <c r="H245" s="3"/>
       <c r="I245" s="8"/>
       <c r="J245" s="8"/>
-      <c r="K245" s="9"/>
-      <c r="L245" s="3"/>
+      <c r="K245" s="10"/>
+      <c r="L245" s="10"/>
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A246" s="5"/>
@@ -4466,8 +4469,8 @@
       <c r="H246" s="3"/>
       <c r="I246" s="8"/>
       <c r="J246" s="8"/>
-      <c r="K246" s="9"/>
-      <c r="L246" s="3"/>
+      <c r="K246" s="10"/>
+      <c r="L246" s="10"/>
     </row>
     <row r="247" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A247" s="5"/>
@@ -4480,8 +4483,8 @@
       <c r="H247" s="3"/>
       <c r="I247" s="8"/>
       <c r="J247" s="8"/>
-      <c r="K247" s="9"/>
-      <c r="L247" s="3"/>
+      <c r="K247" s="10"/>
+      <c r="L247" s="10"/>
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A248" s="5"/>
@@ -4494,8 +4497,8 @@
       <c r="H248" s="3"/>
       <c r="I248" s="8"/>
       <c r="J248" s="8"/>
-      <c r="K248" s="9"/>
-      <c r="L248" s="3"/>
+      <c r="K248" s="10"/>
+      <c r="L248" s="10"/>
     </row>
     <row r="249" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A249" s="5"/>
@@ -4508,8 +4511,8 @@
       <c r="H249" s="3"/>
       <c r="I249" s="8"/>
       <c r="J249" s="8"/>
-      <c r="K249" s="9"/>
-      <c r="L249" s="3"/>
+      <c r="K249" s="10"/>
+      <c r="L249" s="10"/>
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A250" s="5"/>
@@ -4522,8 +4525,8 @@
       <c r="H250" s="3"/>
       <c r="I250" s="8"/>
       <c r="J250" s="8"/>
-      <c r="K250" s="9"/>
-      <c r="L250" s="3"/>
+      <c r="K250" s="10"/>
+      <c r="L250" s="10"/>
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A251" s="5"/>
@@ -4536,8 +4539,8 @@
       <c r="H251" s="3"/>
       <c r="I251" s="8"/>
       <c r="J251" s="8"/>
-      <c r="K251" s="9"/>
-      <c r="L251" s="3"/>
+      <c r="K251" s="10"/>
+      <c r="L251" s="10"/>
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A252" s="5"/>
@@ -4550,8 +4553,8 @@
       <c r="H252" s="3"/>
       <c r="I252" s="8"/>
       <c r="J252" s="8"/>
-      <c r="K252" s="9"/>
-      <c r="L252" s="3"/>
+      <c r="K252" s="10"/>
+      <c r="L252" s="10"/>
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A253" s="5"/>
@@ -4564,8 +4567,8 @@
       <c r="H253" s="3"/>
       <c r="I253" s="8"/>
       <c r="J253" s="8"/>
-      <c r="K253" s="9"/>
-      <c r="L253" s="3"/>
+      <c r="K253" s="10"/>
+      <c r="L253" s="10"/>
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A254" s="5"/>
@@ -4578,8 +4581,8 @@
       <c r="H254" s="3"/>
       <c r="I254" s="8"/>
       <c r="J254" s="8"/>
-      <c r="K254" s="9"/>
-      <c r="L254" s="3"/>
+      <c r="K254" s="10"/>
+      <c r="L254" s="10"/>
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A255" s="5"/>
@@ -4592,8 +4595,8 @@
       <c r="H255" s="3"/>
       <c r="I255" s="8"/>
       <c r="J255" s="8"/>
-      <c r="K255" s="9"/>
-      <c r="L255" s="3"/>
+      <c r="K255" s="10"/>
+      <c r="L255" s="10"/>
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A256" s="5"/>
@@ -4606,8 +4609,8 @@
       <c r="H256" s="3"/>
       <c r="I256" s="8"/>
       <c r="J256" s="8"/>
-      <c r="K256" s="9"/>
-      <c r="L256" s="3"/>
+      <c r="K256" s="10"/>
+      <c r="L256" s="10"/>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A257" s="5"/>
@@ -4620,8 +4623,8 @@
       <c r="H257" s="3"/>
       <c r="I257" s="8"/>
       <c r="J257" s="8"/>
-      <c r="K257" s="9"/>
-      <c r="L257" s="3"/>
+      <c r="K257" s="10"/>
+      <c r="L257" s="10"/>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A258" s="5"/>
@@ -4634,8 +4637,8 @@
       <c r="H258" s="3"/>
       <c r="I258" s="8"/>
       <c r="J258" s="8"/>
-      <c r="K258" s="9"/>
-      <c r="L258" s="3"/>
+      <c r="K258" s="10"/>
+      <c r="L258" s="10"/>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A259" s="5"/>
@@ -4648,8 +4651,8 @@
       <c r="H259" s="3"/>
       <c r="I259" s="8"/>
       <c r="J259" s="8"/>
-      <c r="K259" s="9"/>
-      <c r="L259" s="3"/>
+      <c r="K259" s="10"/>
+      <c r="L259" s="10"/>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A260" s="5"/>
@@ -4662,8 +4665,8 @@
       <c r="H260" s="3"/>
       <c r="I260" s="8"/>
       <c r="J260" s="8"/>
-      <c r="K260" s="9"/>
-      <c r="L260" s="3"/>
+      <c r="K260" s="10"/>
+      <c r="L260" s="10"/>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A261" s="5"/>
@@ -4676,8 +4679,8 @@
       <c r="H261" s="3"/>
       <c r="I261" s="8"/>
       <c r="J261" s="8"/>
-      <c r="K261" s="9"/>
-      <c r="L261" s="3"/>
+      <c r="K261" s="10"/>
+      <c r="L261" s="10"/>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A262" s="5"/>
@@ -4690,8 +4693,8 @@
       <c r="H262" s="3"/>
       <c r="I262" s="8"/>
       <c r="J262" s="8"/>
-      <c r="K262" s="9"/>
-      <c r="L262" s="3"/>
+      <c r="K262" s="10"/>
+      <c r="L262" s="10"/>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A263" s="5"/>
@@ -4704,8 +4707,8 @@
       <c r="H263" s="3"/>
       <c r="I263" s="8"/>
       <c r="J263" s="8"/>
-      <c r="K263" s="9"/>
-      <c r="L263" s="3"/>
+      <c r="K263" s="10"/>
+      <c r="L263" s="10"/>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A264" s="5"/>
@@ -4718,8 +4721,8 @@
       <c r="H264" s="3"/>
       <c r="I264" s="8"/>
       <c r="J264" s="8"/>
-      <c r="K264" s="9"/>
-      <c r="L264" s="3"/>
+      <c r="K264" s="10"/>
+      <c r="L264" s="10"/>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A265" s="5"/>
@@ -4732,8 +4735,8 @@
       <c r="H265" s="3"/>
       <c r="I265" s="8"/>
       <c r="J265" s="8"/>
-      <c r="K265" s="9"/>
-      <c r="L265" s="3"/>
+      <c r="K265" s="10"/>
+      <c r="L265" s="10"/>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A266" s="5"/>
@@ -4746,8 +4749,8 @@
       <c r="H266" s="3"/>
       <c r="I266" s="8"/>
       <c r="J266" s="8"/>
-      <c r="K266" s="9"/>
-      <c r="L266" s="3"/>
+      <c r="K266" s="10"/>
+      <c r="L266" s="10"/>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A267" s="5"/>
@@ -4760,8 +4763,8 @@
       <c r="H267" s="3"/>
       <c r="I267" s="8"/>
       <c r="J267" s="8"/>
-      <c r="K267" s="9"/>
-      <c r="L267" s="3"/>
+      <c r="K267" s="10"/>
+      <c r="L267" s="10"/>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A268" s="5"/>
@@ -4774,8 +4777,8 @@
       <c r="H268" s="3"/>
       <c r="I268" s="8"/>
       <c r="J268" s="8"/>
-      <c r="K268" s="9"/>
-      <c r="L268" s="3"/>
+      <c r="K268" s="10"/>
+      <c r="L268" s="10"/>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A269" s="5"/>
@@ -4788,8 +4791,8 @@
       <c r="H269" s="3"/>
       <c r="I269" s="8"/>
       <c r="J269" s="8"/>
-      <c r="K269" s="9"/>
-      <c r="L269" s="3"/>
+      <c r="K269" s="10"/>
+      <c r="L269" s="10"/>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A270" s="5"/>
@@ -4802,8 +4805,8 @@
       <c r="H270" s="3"/>
       <c r="I270" s="8"/>
       <c r="J270" s="8"/>
-      <c r="K270" s="9"/>
-      <c r="L270" s="3"/>
+      <c r="K270" s="10"/>
+      <c r="L270" s="10"/>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A271" s="5"/>
@@ -4816,8 +4819,8 @@
       <c r="H271" s="3"/>
       <c r="I271" s="8"/>
       <c r="J271" s="8"/>
-      <c r="K271" s="9"/>
-      <c r="L271" s="3"/>
+      <c r="K271" s="10"/>
+      <c r="L271" s="10"/>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A272" s="5"/>
@@ -4830,8 +4833,8 @@
       <c r="H272" s="3"/>
       <c r="I272" s="8"/>
       <c r="J272" s="8"/>
-      <c r="K272" s="9"/>
-      <c r="L272" s="3"/>
+      <c r="K272" s="10"/>
+      <c r="L272" s="10"/>
     </row>
     <row r="273" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A273" s="5"/>
@@ -4844,8 +4847,8 @@
       <c r="H273" s="3"/>
       <c r="I273" s="8"/>
       <c r="J273" s="8"/>
-      <c r="K273" s="9"/>
-      <c r="L273" s="3"/>
+      <c r="K273" s="10"/>
+      <c r="L273" s="10"/>
     </row>
     <row r="274" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A274" s="5"/>
@@ -4858,8 +4861,8 @@
       <c r="H274" s="3"/>
       <c r="I274" s="8"/>
       <c r="J274" s="8"/>
-      <c r="K274" s="9"/>
-      <c r="L274" s="3"/>
+      <c r="K274" s="10"/>
+      <c r="L274" s="10"/>
     </row>
     <row r="275" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A275" s="5"/>
@@ -4872,8 +4875,8 @@
       <c r="H275" s="3"/>
       <c r="I275" s="8"/>
       <c r="J275" s="8"/>
-      <c r="K275" s="9"/>
-      <c r="L275" s="3"/>
+      <c r="K275" s="10"/>
+      <c r="L275" s="10"/>
     </row>
     <row r="276" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A276" s="5"/>
@@ -4886,8 +4889,8 @@
       <c r="H276" s="3"/>
       <c r="I276" s="8"/>
       <c r="J276" s="8"/>
-      <c r="K276" s="9"/>
-      <c r="L276" s="3"/>
+      <c r="K276" s="10"/>
+      <c r="L276" s="10"/>
     </row>
     <row r="277" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A277" s="5"/>
@@ -4900,8 +4903,8 @@
       <c r="H277" s="3"/>
       <c r="I277" s="8"/>
       <c r="J277" s="8"/>
-      <c r="K277" s="9"/>
-      <c r="L277" s="3"/>
+      <c r="K277" s="10"/>
+      <c r="L277" s="10"/>
     </row>
     <row r="278" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A278" s="5"/>
@@ -4914,8 +4917,8 @@
       <c r="H278" s="3"/>
       <c r="I278" s="8"/>
       <c r="J278" s="8"/>
-      <c r="K278" s="9"/>
-      <c r="L278" s="3"/>
+      <c r="K278" s="10"/>
+      <c r="L278" s="10"/>
     </row>
     <row r="279" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A279" s="5"/>
@@ -4928,8 +4931,8 @@
       <c r="H279" s="3"/>
       <c r="I279" s="8"/>
       <c r="J279" s="8"/>
-      <c r="K279" s="9"/>
-      <c r="L279" s="3"/>
+      <c r="K279" s="10"/>
+      <c r="L279" s="10"/>
     </row>
     <row r="280" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A280" s="5"/>
@@ -4942,8 +4945,8 @@
       <c r="H280" s="3"/>
       <c r="I280" s="8"/>
       <c r="J280" s="8"/>
-      <c r="K280" s="9"/>
-      <c r="L280" s="3"/>
+      <c r="K280" s="10"/>
+      <c r="L280" s="10"/>
     </row>
     <row r="281" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A281" s="5"/>
@@ -4956,8 +4959,8 @@
       <c r="H281" s="3"/>
       <c r="I281" s="8"/>
       <c r="J281" s="8"/>
-      <c r="K281" s="9"/>
-      <c r="L281" s="3"/>
+      <c r="K281" s="10"/>
+      <c r="L281" s="10"/>
     </row>
     <row r="282" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A282" s="5"/>
@@ -4970,8 +4973,8 @@
       <c r="H282" s="3"/>
       <c r="I282" s="8"/>
       <c r="J282" s="8"/>
-      <c r="K282" s="9"/>
-      <c r="L282" s="3"/>
+      <c r="K282" s="10"/>
+      <c r="L282" s="10"/>
     </row>
     <row r="283" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A283" s="5"/>
@@ -4984,8 +4987,8 @@
       <c r="H283" s="3"/>
       <c r="I283" s="8"/>
       <c r="J283" s="8"/>
-      <c r="K283" s="9"/>
-      <c r="L283" s="3"/>
+      <c r="K283" s="10"/>
+      <c r="L283" s="10"/>
     </row>
     <row r="284" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A284" s="5"/>
@@ -4998,8 +5001,8 @@
       <c r="H284" s="3"/>
       <c r="I284" s="8"/>
       <c r="J284" s="8"/>
-      <c r="K284" s="9"/>
-      <c r="L284" s="3"/>
+      <c r="K284" s="10"/>
+      <c r="L284" s="10"/>
     </row>
     <row r="285" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A285" s="5"/>
@@ -5012,8 +5015,8 @@
       <c r="H285" s="3"/>
       <c r="I285" s="8"/>
       <c r="J285" s="8"/>
-      <c r="K285" s="9"/>
-      <c r="L285" s="3"/>
+      <c r="K285" s="10"/>
+      <c r="L285" s="10"/>
     </row>
     <row r="286" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A286" s="5"/>
@@ -5026,8 +5029,8 @@
       <c r="H286" s="3"/>
       <c r="I286" s="8"/>
       <c r="J286" s="8"/>
-      <c r="K286" s="9"/>
-      <c r="L286" s="3"/>
+      <c r="K286" s="10"/>
+      <c r="L286" s="10"/>
     </row>
     <row r="287" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A287" s="5"/>
@@ -5040,8 +5043,8 @@
       <c r="H287" s="3"/>
       <c r="I287" s="8"/>
       <c r="J287" s="8"/>
-      <c r="K287" s="9"/>
-      <c r="L287" s="3"/>
+      <c r="K287" s="10"/>
+      <c r="L287" s="10"/>
     </row>
     <row r="288" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A288" s="5"/>
@@ -5054,8 +5057,8 @@
       <c r="H288" s="3"/>
       <c r="I288" s="8"/>
       <c r="J288" s="8"/>
-      <c r="K288" s="9"/>
-      <c r="L288" s="3"/>
+      <c r="K288" s="10"/>
+      <c r="L288" s="10"/>
     </row>
     <row r="289" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A289" s="5"/>
@@ -5068,8 +5071,8 @@
       <c r="H289" s="3"/>
       <c r="I289" s="8"/>
       <c r="J289" s="8"/>
-      <c r="K289" s="9"/>
-      <c r="L289" s="3"/>
+      <c r="K289" s="10"/>
+      <c r="L289" s="10"/>
     </row>
     <row r="290" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A290" s="5"/>
@@ -5082,8 +5085,8 @@
       <c r="H290" s="3"/>
       <c r="I290" s="8"/>
       <c r="J290" s="8"/>
-      <c r="K290" s="9"/>
-      <c r="L290" s="3"/>
+      <c r="K290" s="10"/>
+      <c r="L290" s="10"/>
     </row>
     <row r="291" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A291" s="5"/>
@@ -5096,8 +5099,8 @@
       <c r="H291" s="3"/>
       <c r="I291" s="8"/>
       <c r="J291" s="8"/>
-      <c r="K291" s="9"/>
-      <c r="L291" s="3"/>
+      <c r="K291" s="10"/>
+      <c r="L291" s="10"/>
     </row>
     <row r="292" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A292" s="5"/>
@@ -5110,8 +5113,8 @@
       <c r="H292" s="3"/>
       <c r="I292" s="8"/>
       <c r="J292" s="8"/>
-      <c r="K292" s="9"/>
-      <c r="L292" s="3"/>
+      <c r="K292" s="10"/>
+      <c r="L292" s="10"/>
     </row>
     <row r="293" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A293" s="5"/>
@@ -5124,8 +5127,8 @@
       <c r="H293" s="3"/>
       <c r="I293" s="8"/>
       <c r="J293" s="8"/>
-      <c r="K293" s="9"/>
-      <c r="L293" s="3"/>
+      <c r="K293" s="10"/>
+      <c r="L293" s="10"/>
     </row>
     <row r="294" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A294" s="5"/>
@@ -5138,8 +5141,8 @@
       <c r="H294" s="3"/>
       <c r="I294" s="8"/>
       <c r="J294" s="8"/>
-      <c r="K294" s="9"/>
-      <c r="L294" s="3"/>
+      <c r="K294" s="10"/>
+      <c r="L294" s="10"/>
     </row>
     <row r="295" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A295" s="5"/>
@@ -5152,8 +5155,8 @@
       <c r="H295" s="3"/>
       <c r="I295" s="8"/>
       <c r="J295" s="8"/>
-      <c r="K295" s="9"/>
-      <c r="L295" s="3"/>
+      <c r="K295" s="10"/>
+      <c r="L295" s="10"/>
     </row>
     <row r="296" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A296" s="5"/>
@@ -5166,8 +5169,8 @@
       <c r="H296" s="3"/>
       <c r="I296" s="8"/>
       <c r="J296" s="8"/>
-      <c r="K296" s="9"/>
-      <c r="L296" s="3"/>
+      <c r="K296" s="10"/>
+      <c r="L296" s="10"/>
     </row>
     <row r="297" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A297" s="5"/>
@@ -5180,8 +5183,8 @@
       <c r="H297" s="3"/>
       <c r="I297" s="8"/>
       <c r="J297" s="8"/>
-      <c r="K297" s="9"/>
-      <c r="L297" s="3"/>
+      <c r="K297" s="10"/>
+      <c r="L297" s="10"/>
     </row>
     <row r="298" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A298" s="5"/>
@@ -5194,8 +5197,8 @@
       <c r="H298" s="3"/>
       <c r="I298" s="8"/>
       <c r="J298" s="8"/>
-      <c r="K298" s="9"/>
-      <c r="L298" s="3"/>
+      <c r="K298" s="10"/>
+      <c r="L298" s="10"/>
     </row>
     <row r="299" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A299" s="5"/>
@@ -5208,8 +5211,8 @@
       <c r="H299" s="3"/>
       <c r="I299" s="8"/>
       <c r="J299" s="8"/>
-      <c r="K299" s="9"/>
-      <c r="L299" s="3"/>
+      <c r="K299" s="10"/>
+      <c r="L299" s="10"/>
     </row>
     <row r="300" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A300" s="5"/>
@@ -5222,8 +5225,8 @@
       <c r="H300" s="3"/>
       <c r="I300" s="8"/>
       <c r="J300" s="8"/>
-      <c r="K300" s="9"/>
-      <c r="L300" s="3"/>
+      <c r="K300" s="10"/>
+      <c r="L300" s="10"/>
     </row>
     <row r="301" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A301" s="5"/>
@@ -5236,8 +5239,8 @@
       <c r="H301" s="3"/>
       <c r="I301" s="8"/>
       <c r="J301" s="8"/>
-      <c r="K301" s="9"/>
-      <c r="L301" s="3"/>
+      <c r="K301" s="3"/>
+      <c r="L301" s="9"/>
     </row>
     <row r="302" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A302" s="1"/>
